--- a/hira_material_automation/output/monthly/202601_202605__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>1359</t>
@@ -519,7 +523,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>1307</t>
@@ -552,7 +560,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>1483</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:07:06</t>
+          <t>2026-05-14T22:15:20</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e39d107772a33067e4024bdef7441ad0b0b1c502886a4127b5662faf4fcd1803</t>
+          <t>0a3c427f439bfa9ba21434d46f67135c96c56a36cf864e3ed7e642c3ac7728fd</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:15:20</t>
+          <t>2026-05-24T22:00:01</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0a3c427f439bfa9ba21434d46f67135c96c56a36cf864e3ed7e642c3ac7728fd</t>
+          <t>90825dc8a6c30fc7e744969800ed6c7436d0f6b5c98b93561b38df9fb633ca59</t>
         </is>
       </c>
     </row>
